--- a/data/trans_dic/IP2001-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2001-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que tienen caries</t>
+          <t>Menores que tienen caries (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,7; 22,76</t>
+          <t>9,26; 21,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,29; 18,13</t>
+          <t>6,98; 18,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,92; 28,76</t>
+          <t>10,91; 28,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,86; 23,28</t>
+          <t>9,63; 23,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,09; 25,01</t>
+          <t>10,8; 24,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,71; 22,76</t>
+          <t>8,3; 23,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 12,98</t>
+          <t>1,55; 13,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,44; 20,06</t>
+          <t>11,04; 20,43</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,62; 18,93</t>
+          <t>10,28; 18,89</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,67; 22,66</t>
+          <t>11,58; 22,89</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 7,14</t>
+          <t>0,8; 7,42</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,8; 11,62</t>
+          <t>6,83; 11,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,63; 13,84</t>
+          <t>8,49; 13,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,87; 13,61</t>
+          <t>8,95; 14,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,65</t>
+          <t>3,09; 6,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,23; 8,99</t>
+          <t>5,34; 9,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,36; 12,32</t>
+          <t>7,61; 12,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,76; 12,46</t>
+          <t>7,84; 12,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,75; 7,75</t>
+          <t>3,8; 7,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,51; 9,41</t>
+          <t>6,41; 9,41</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,77; 12,13</t>
+          <t>8,55; 12,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,76; 12,13</t>
+          <t>8,89; 12,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,97; 6,47</t>
+          <t>4,02; 6,74</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,67</t>
+          <t>1,66; 6,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 6,97</t>
+          <t>1,76; 7,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,44; 10,16</t>
+          <t>3,5; 9,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 9,0</t>
+          <t>2,6; 8,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,87; 10,79</t>
+          <t>4,0; 11,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 8,66</t>
+          <t>2,04; 8,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,57; 11,42</t>
+          <t>4,32; 11,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,3; 12,15</t>
+          <t>4,58; 12,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 7,61</t>
+          <t>3,27; 7,57</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 6,54</t>
+          <t>2,67; 6,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,47; 9,22</t>
+          <t>4,72; 9,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 9,32</t>
+          <t>4,13; 9,29</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,75; 10,33</t>
+          <t>6,72; 10,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,43; 11,02</t>
+          <t>7,74; 11,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,53; 12,58</t>
+          <t>8,71; 12,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 5,95</t>
+          <t>3,15; 5,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,36; 9,64</t>
+          <t>6,35; 9,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,89; 11,5</t>
+          <t>7,72; 11,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,9; 11,71</t>
+          <t>7,95; 11,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,86</t>
+          <t>4,47; 7,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,07; 9,44</t>
+          <t>7,07; 9,55</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,13; 10,78</t>
+          <t>8,1; 10,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,8; 11,57</t>
+          <t>8,85; 11,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,28; 6,39</t>
+          <t>4,17; 6,36</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que tienen caries (tasa de respuesta: 99,49%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>13138</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10379</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10425</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>12769</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13968</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>9846</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2956</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>25907</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>24347</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>20271</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2956</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>8054; 18975</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6140; 16574</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6197; 16415</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7771; 18765</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>8922; 20578</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>5590; 15636</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>929; 8082</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>18504; 34250</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>17535; 32231</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>14383; 28429</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>909; 8427</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>35169</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>45040</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>48860</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>21267</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>31376</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>44884</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>45757</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>28021</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>66545</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>89924</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>94616</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>49288</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>26868; 45911</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>35342; 55678</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>39333; 61793</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>13972; 29888</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>24045; 41521</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>35186; 57187</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>36312; 57846</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>19151; 39627</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>54085; 79419</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>75132; 106323</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>80221; 110882</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>38429; 64449</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>5870</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6076</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9897</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7187</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>9942</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>12351</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>13781</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>15812</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>13182</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>22249</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>20968</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2673; 11021</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2736; 10937</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5688; 15543</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3822; 12444</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5847; 16866</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3173; 12717</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>7313; 18961</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>8338; 22832</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>10060; 23273</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>8296; 20588</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>15665; 30705</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>13589; 30594</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>54177</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>61495</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>69182</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>28454</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>54087</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>65958</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>67954</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>44758</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>108265</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>127453</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>137136</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>73212</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>43146; 66270</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>51020; 77399</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>57365; 83173</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>20572; 38658</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>42973; 65718</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>54034; 80453</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>55615; 82868</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>33339; 57334</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>93237; 125975</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>110064; 149192</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>120256; 155821</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>58316; 88997</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2001-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2001-Estudios-trans_dic.xlsx
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,26; 21,82</t>
+          <t>9,47; 21,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,98; 18,83</t>
+          <t>7,3; 18,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,91; 28,89</t>
+          <t>10,95; 27,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,63; 23,26</t>
+          <t>9,92; 22,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,8; 24,91</t>
+          <t>10,72; 25,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,3; 23,21</t>
+          <t>9,09; 22,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 13,51</t>
+          <t>1,56; 14,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,04; 20,43</t>
+          <t>11,54; 20,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,28; 18,89</t>
+          <t>10,31; 19,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,58; 22,89</t>
+          <t>11,71; 22,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,42</t>
+          <t>0,82; 7,02</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 11,66</t>
+          <t>6,56; 11,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,49; 13,38</t>
+          <t>8,51; 13,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,95; 14,07</t>
+          <t>8,65; 13,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,09; 6,61</t>
+          <t>3,14; 6,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,34; 9,22</t>
+          <t>5,23; 9,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,61; 12,37</t>
+          <t>7,54; 12,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,84; 12,49</t>
+          <t>7,71; 12,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,8; 7,86</t>
+          <t>4,01; 7,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,41; 9,41</t>
+          <t>6,47; 9,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,55; 12,1</t>
+          <t>8,56; 12,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,89; 12,29</t>
+          <t>8,88; 12,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,02; 6,74</t>
+          <t>3,98; 6,72</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 6,83</t>
+          <t>1,8; 6,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 7,05</t>
+          <t>1,78; 7,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,5; 9,55</t>
+          <t>3,69; 10,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 8,46</t>
+          <t>2,51; 8,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 11,55</t>
+          <t>4,01; 11,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 8,19</t>
+          <t>2,23; 8,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,32; 11,21</t>
+          <t>4,44; 10,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,58; 12,54</t>
+          <t>4,63; 12,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,27; 7,57</t>
+          <t>3,39; 7,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 6,63</t>
+          <t>2,69; 6,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,72; 9,25</t>
+          <t>4,58; 9,15</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,13; 9,29</t>
+          <t>4,3; 9,34</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,72; 10,32</t>
+          <t>6,78; 10,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,74; 11,74</t>
+          <t>7,47; 11,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,71; 12,62</t>
+          <t>8,7; 12,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 5,92</t>
+          <t>3,14; 5,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,35; 9,71</t>
+          <t>6,53; 9,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,72; 11,49</t>
+          <t>7,56; 11,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,95; 11,84</t>
+          <t>7,93; 11,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,47; 7,69</t>
+          <t>4,39; 7,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,07; 9,55</t>
+          <t>7,17; 9,47</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,1; 10,97</t>
+          <t>8,11; 10,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,85; 11,47</t>
+          <t>8,8; 11,32</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,17; 6,36</t>
+          <t>4,2; 6,42</t>
         </is>
       </c>
     </row>
@@ -1504,17 +1504,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8054; 18975</t>
+          <t>8237; 18975</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6140; 16574</t>
+          <t>6421; 15900</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6197; 16415</t>
+          <t>6223; 15673</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1524,42 +1524,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7771; 18765</t>
+          <t>8005; 18385</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8922; 20578</t>
+          <t>8858; 21384</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5590; 15636</t>
+          <t>6122; 15236</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>929; 8082</t>
+          <t>934; 8412</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18504; 34250</t>
+          <t>19342; 34399</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17535; 32231</t>
+          <t>17600; 32680</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14383; 28429</t>
+          <t>14545; 27570</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>909; 8427</t>
+          <t>929; 7969</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26868; 45911</t>
+          <t>25823; 45256</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35342; 55678</t>
+          <t>35415; 56397</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39333; 61793</t>
+          <t>38021; 59606</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13972; 29888</t>
+          <t>14205; 29520</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24045; 41521</t>
+          <t>23543; 41079</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35186; 57187</t>
+          <t>34882; 57236</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36312; 57846</t>
+          <t>35696; 56965</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19151; 39627</t>
+          <t>20220; 40240</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>54085; 79419</t>
+          <t>54628; 78963</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75132; 106323</t>
+          <t>75170; 106707</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>80221; 110882</t>
+          <t>80141; 110552</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38429; 64449</t>
+          <t>38074; 64260</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2673; 11021</t>
+          <t>2901; 10715</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2736; 10937</t>
+          <t>2754; 10975</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5688; 15543</t>
+          <t>6001; 16376</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3822; 12444</t>
+          <t>3699; 12119</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5847; 16866</t>
+          <t>5857; 16646</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3173; 12717</t>
+          <t>3462; 12651</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7313; 18961</t>
+          <t>7515; 18514</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8338; 22832</t>
+          <t>8430; 23038</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10060; 23273</t>
+          <t>10417; 23467</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8296; 20588</t>
+          <t>8364; 19969</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15665; 30705</t>
+          <t>15194; 30363</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13589; 30594</t>
+          <t>14151; 30733</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>43146; 66270</t>
+          <t>43502; 66367</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51020; 77399</t>
+          <t>49264; 74585</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>57365; 83173</t>
+          <t>57351; 81317</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20572; 38658</t>
+          <t>20503; 38040</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42973; 65718</t>
+          <t>44185; 67528</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>54034; 80453</t>
+          <t>52945; 80410</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>55615; 82868</t>
+          <t>55501; 82084</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33339; 57334</t>
+          <t>32717; 57977</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93237; 125975</t>
+          <t>94570; 124900</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>110064; 149192</t>
+          <t>110265; 147580</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>120256; 155821</t>
+          <t>119580; 153733</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>58316; 88997</t>
+          <t>58732; 89839</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2001-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2001-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,44 +649,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15,83%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16,9%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14,61%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>15,11%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11,79%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>18,35%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15,83%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>16,9%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,61%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>15,46%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,47; 21,82</t>
+          <t>9,86; 23,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,3; 18,07</t>
+          <t>11,09; 25,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,95; 27,59</t>
+          <t>8,71; 22,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>1,65; 13,58</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>9,7; 22,76</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7,29; 18,13</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>10,92; 28,76</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>9,92; 22,79</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10,72; 25,88</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9,09; 22,61</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1,56; 14,07</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,54; 20,52</t>
+          <t>11,44; 20,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,31; 19,15</t>
+          <t>9,62; 18,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,71; 22,2</t>
+          <t>11,67; 22,66</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,02</t>
+          <t>0,92; 7,91</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,97%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9,88%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5,67%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>8,94%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>10,82%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>11,12%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,97%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,88%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,56; 11,5</t>
+          <t>5,23; 8,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,51; 13,55</t>
+          <t>7,36; 12,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,65; 13,57</t>
+          <t>7,76; 12,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 6,53</t>
+          <t>3,88; 7,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,23; 9,13</t>
+          <t>6,8; 11,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,54; 12,38</t>
+          <t>8,63; 13,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,71; 12,3</t>
+          <t>8,87; 13,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,01; 7,98</t>
+          <t>3,51; 7,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,47; 9,36</t>
+          <t>6,51; 9,41</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,56; 12,15</t>
+          <t>8,77; 12,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,88; 12,25</t>
+          <t>8,76; 12,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 6,72</t>
+          <t>4,24; 6,69</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,81%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7,89%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3,64%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,92%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6,08%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 6,64</t>
+          <t>3,87; 10,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 7,08</t>
+          <t>2,19; 8,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,69; 10,06</t>
+          <t>4,57; 11,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 8,24</t>
+          <t>4,53; 12,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 11,4</t>
+          <t>1,74; 6,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 8,15</t>
+          <t>1,73; 6,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,44; 10,95</t>
+          <t>3,44; 10,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 12,65</t>
+          <t>2,63; 8,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 7,64</t>
+          <t>3,2; 7,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 6,43</t>
+          <t>2,6; 6,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,58; 9,15</t>
+          <t>4,47; 9,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,3; 9,34</t>
+          <t>4,37; 9,34</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7,99%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,42%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>8,44%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9,33%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>10,5%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,99%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,42%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,78; 10,34</t>
+          <t>6,36; 9,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,47; 11,31</t>
+          <t>7,89; 11,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,7; 12,34</t>
+          <t>7,9; 11,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 5,83</t>
+          <t>4,65; 8,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,53; 9,98</t>
+          <t>6,75; 10,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,56; 11,48</t>
+          <t>7,43; 11,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,93; 11,73</t>
+          <t>8,53; 12,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 7,77</t>
+          <t>3,37; 6,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,17; 9,47</t>
+          <t>7,07; 9,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,11; 10,86</t>
+          <t>8,13; 10,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,8; 11,32</t>
+          <t>8,8; 11,57</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,2; 6,42</t>
+          <t>4,55; 6,71</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,44 +1436,44 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12769</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13968</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9846</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>13138</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>10379</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>10425</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>12769</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>13968</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9846</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2956</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
           <t>25907</t>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>2924</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8237; 18975</t>
+          <t>7956; 18779</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6421; 15900</t>
+          <t>9163; 20661</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6223; 15673</t>
+          <t>5866; 15331</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>907; 7459</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>8430; 19787</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>6412; 15960</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6203; 16337</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8005; 18385</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8858; 21384</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6122; 15236</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>934; 8412</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19342; 34399</t>
+          <t>19170; 33626</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17600; 32680</t>
+          <t>16421; 32295</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14545; 27570</t>
+          <t>14493; 28138</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>929; 7969</t>
+          <t>931; 7980</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>31376</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>44884</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>45757</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>26370</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>35169</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>45040</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>48860</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>21267</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>31376</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>44884</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>45757</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>28021</t>
+          <t>21567</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>49288</t>
+          <t>47937</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25823; 45256</t>
+          <t>23563; 40466</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35415; 56397</t>
+          <t>34006; 56951</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38021; 59606</t>
+          <t>35959; 57728</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14205; 29520</t>
+          <t>18075; 37115</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23543; 41079</t>
+          <t>26754; 45727</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34882; 57236</t>
+          <t>35904; 57583</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35696; 56965</t>
+          <t>38969; 59794</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20220; 40240</t>
+          <t>14929; 30028</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>54628; 78963</t>
+          <t>54940; 79363</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75170; 106707</t>
+          <t>77038; 106595</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>80141; 110552</t>
+          <t>79035; 109511</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38074; 64260</t>
+          <t>37718; 59543</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>9942</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12351</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>13208</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>5870</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>6076</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>9897</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7187</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>9942</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7106</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>12351</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>6958</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20968</t>
+          <t>20166</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2901; 10715</t>
+          <t>5646; 15749</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2754; 10975</t>
+          <t>3396; 13442</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6001; 16376</t>
+          <t>7727; 19313</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3699; 12119</t>
+          <t>7581; 21242</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5857; 16646</t>
+          <t>2810; 10762</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3462; 12651</t>
+          <t>2684; 10808</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7515; 18514</t>
+          <t>5598; 16532</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8430; 23038</t>
+          <t>3896; 12783</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10417; 23467</t>
+          <t>9846; 23381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8364; 19969</t>
+          <t>8081; 20312</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15194; 30363</t>
+          <t>14840; 30608</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14151; 30733</t>
+          <t>13767; 29460</t>
         </is>
       </c>
     </row>
@@ -1997,37 +1997,37 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>44</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>54087</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>65958</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>67954</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>42502</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>54177</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>61495</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>69182</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>28454</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>54087</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>65958</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>67954</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>44758</t>
+          <t>28525</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73212</t>
+          <t>71027</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>43502; 66367</t>
+          <t>43065; 65260</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>49264; 74585</t>
+          <t>55249; 80516</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>57351; 81317</t>
+          <t>55272; 81936</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20503; 38040</t>
+          <t>31994; 56115</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44185; 67528</t>
+          <t>43339; 66323</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>52945; 80410</t>
+          <t>48968; 72618</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>55501; 82084</t>
+          <t>56179; 82855</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32717; 57977</t>
+          <t>20833; 38301</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>94570; 124900</t>
+          <t>93217; 124482</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>110265; 147580</t>
+          <t>110562; 146583</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>119580; 153733</t>
+          <t>119570; 157149</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>58732; 89839</t>
+          <t>59455; 87653</t>
         </is>
       </c>
     </row>
